--- a/paper_trading_lay0x1/sinais_lay0x1_gold_2026-07-13.xlsx
+++ b/paper_trading_lay0x1/sinais_lay0x1_gold_2026-07-13.xlsx
@@ -1,127 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/paper_trading_lay0x1/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_2B593D9757E9EF246D20C2F0509BF8F379B3FAE2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{067BA845-5318-4DA2-9D0B-B33A839411EE}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sinais" sheetId="1" r:id="rId1"/>
+    <sheet name="Sinais" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Horario</t>
-  </si>
-  <si>
-    <t>Liga</t>
-  </si>
-  <si>
-    <t>Mandante</t>
-  </si>
-  <si>
-    <t>Visitante</t>
-  </si>
-  <si>
-    <t>Metodo</t>
-  </si>
-  <si>
-    <t>Prob</t>
-  </si>
-  <si>
-    <t>Odd_lay_entrada</t>
-  </si>
-  <si>
-    <t>PREENCHER_odd_abertura</t>
-  </si>
-  <si>
-    <t>PREENCHER_odd_min60</t>
-  </si>
-  <si>
-    <t>PREENCHER_odd_min75</t>
-  </si>
-  <si>
-    <t>Placar_final</t>
-  </si>
-  <si>
-    <t>Momento_gols</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>obs</t>
-  </si>
-  <si>
-    <t>2026-07-13</t>
-  </si>
-  <si>
-    <t>RF</t>
-  </si>
-  <si>
-    <t>AGUARDA</t>
-  </si>
-  <si>
-    <t>20:30:00</t>
-  </si>
-  <si>
-    <t>BRAZIL 2</t>
-  </si>
-  <si>
-    <t>Ceara SC Fortaleza</t>
-  </si>
-  <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
-    <t>19:00:00</t>
-  </si>
-  <si>
-    <t>America MG</t>
-  </si>
-  <si>
-    <t>Londrina</t>
-  </si>
-  <si>
-    <t>BRAZIL 3</t>
-  </si>
-  <si>
-    <t>Figueirense</t>
-  </si>
-  <si>
-    <t>Volta Redonda</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -140,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -442,142 +408,94 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Horário</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Liga</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Mandante</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Odd Lay Betfair</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Probabilidade ML</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Estratégia</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2">
-        <v>93.4</v>
-      </c>
-      <c r="H2">
-        <v>14.5</v>
-      </c>
-      <c r="N2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3">
-        <v>93.8</v>
-      </c>
-      <c r="H3">
-        <v>15</v>
-      </c>
-      <c r="N3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4">
-        <v>93.6</v>
-      </c>
-      <c r="H4">
-        <v>15</v>
-      </c>
-      <c r="N4" t="s">
-        <v>17</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>BRAZIL 3</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Volta Redonda</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>94.2%</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Random Forest (RF)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/paper_trading_lay0x1/sinais_lay0x1_gold_2026-07-13.xlsx
+++ b/paper_trading_lay0x1/sinais_lay0x1_gold_2026-07-13.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sinais" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,48 +425,63 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Horário</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Liga</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Mandante</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Visitante</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Odd Lay Betfair</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Probabilidade ML</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Estratégia</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lucro (R$)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Placar Final</t>
         </is>
       </c>
     </row>
@@ -495,6 +522,19 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>Random Forest (RF)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0-0</t>
         </is>
       </c>
     </row>
